--- a/examples/Config/Excel/Server/SceneConfig.xlsx
+++ b/examples/Config/Excel/Server/SceneConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sining/Code/Git/Fantasy/Examples/Config/Excel/Server/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FantasyNi\examples\Config\Excel\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA0EE65-381D-9A46-BF76-3AF2421B0D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E6A6AE-834A-493B-AAED-0AE30F3EFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-900" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33132" yWindow="1092" windowWidth="25296" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneConfig" sheetId="8" r:id="rId1"/>
@@ -22,18 +22,6 @@
     <definedName name="SceneTypeList">#REF!:INDEX(#REF!, MATCH(9.99999999999999E+307,#REF!))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -51,7 +39,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>由于改表格使用了公式。</t>
         </r>
@@ -61,7 +50,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -72,7 +62,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>所以不要改动列的位置。</t>
         </r>
@@ -81,7 +72,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -96,7 +88,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Id</t>
         </r>
@@ -106,7 +99,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>计算规则</t>
         </r>
@@ -116,7 +110,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">:
 </t>
@@ -127,7 +122,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1</t>
         </r>
@@ -137,7 +133,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>：</t>
         </r>
@@ -147,7 +144,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Id</t>
         </r>
@@ -157,7 +155,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>不能小于当前</t>
         </r>
@@ -167,7 +166,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>WorldConfigId * 1000 +1</t>
         </r>
@@ -177,7 +177,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>。</t>
         </r>
@@ -187,7 +188,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -198,7 +200,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2:  Id</t>
         </r>
@@ -208,7 +211,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>不能大于当前</t>
         </r>
@@ -218,7 +222,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>WorldConfigId * 1000 +255</t>
         </r>
@@ -228,7 +233,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>。</t>
         </r>
@@ -238,7 +244,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -249,7 +256,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>3</t>
         </r>
@@ -259,7 +267,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>：</t>
         </r>
@@ -269,7 +278,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Id</t>
         </r>
@@ -279,7 +289,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>必须在</t>
         </r>
@@ -289,7 +300,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1</t>
         </r>
@@ -299,7 +311,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>和</t>
         </r>
@@ -309,7 +322,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2</t>
         </r>
@@ -319,7 +333,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>条件之间。</t>
         </r>
@@ -333,7 +348,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>ProcessConfig</t>
         </r>
@@ -343,7 +359,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>表的</t>
         </r>
@@ -353,7 +370,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Id
 </t>
@@ -364,7 +382,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>一个进程下有多少个</t>
         </r>
@@ -374,7 +393,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -388,7 +408,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>关联</t>
         </r>
@@ -398,7 +419,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>WorldConfig</t>
         </r>
@@ -408,7 +430,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>表（</t>
         </r>
@@ -418,7 +441,8 @@
             <sz val="10"/>
             <color rgb="FFFF0000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>不能为空）</t>
         </r>
@@ -428,7 +452,8 @@
             <sz val="10"/>
             <color rgb="FFFF0000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -439,7 +464,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用于表示这个</t>
         </r>
@@ -449,7 +475,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -459,7 +486,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>属于哪个世界，</t>
         </r>
@@ -469,7 +497,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Fantasy</t>
         </r>
@@ -479,7 +508,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>里的世界可以理解为游戏的一个区。</t>
         </r>
@@ -489,7 +519,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -500,7 +531,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>这样就可以设置出一个进程下同时运行多个区，也是一个压缩服务器成本的一个手段</t>
         </r>
@@ -514,7 +546,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用于配置</t>
         </r>
@@ -524,7 +557,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -534,7 +568,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>在框架中运行的方式：</t>
         </r>
@@ -544,7 +579,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -566,7 +602,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>:</t>
         </r>
@@ -576,7 +613,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>设置</t>
         </r>
@@ -586,7 +624,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -596,7 +635,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>在当前进程的主线程中运行、如果多个</t>
         </r>
@@ -606,7 +646,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -616,7 +657,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>在同一个</t>
         </r>
@@ -626,7 +668,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>ProcessConfigId</t>
         </r>
@@ -636,7 +679,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>下，表示这些</t>
         </r>
@@ -646,7 +690,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -656,7 +701,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>都是在同一个主线程中运行。如果想提升效率可以配置多个进程（也就是</t>
         </r>
@@ -666,7 +712,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Process</t>
         </r>
@@ -676,7 +723,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>）分别对应多个</t>
         </r>
@@ -686,7 +734,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -696,7 +745,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>，这样设置就是多进程单线程的配置方法。</t>
         </r>
@@ -706,7 +756,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -985,7 +1036,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用来表示这个</t>
         </r>
@@ -995,7 +1047,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1005,7 +1058,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>是什么类型，这样可以在框架中的</t>
         </r>
@@ -1015,7 +1069,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>OnSceneCreate</t>
         </r>
@@ -1025,7 +1080,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>的事件中根据</t>
         </r>
@@ -1035,7 +1091,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SceneType</t>
         </r>
@@ -1045,7 +1102,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>来添加不同的组件，而达到不同</t>
         </r>
@@ -1055,7 +1113,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1065,7 +1124,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>功能不一样的效果。</t>
         </r>
@@ -1075,7 +1135,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1086,7 +1147,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>比如鉴权</t>
         </r>
@@ -1096,7 +1158,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1106,7 +1169,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>和聊天</t>
         </r>
@@ -1116,7 +1180,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1126,7 +1191,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>、通过这个就可以知道当前这个</t>
         </r>
@@ -1136,7 +1202,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1146,7 +1213,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>是什么类型了，这样在创建的时候根据不同类型添加不同的组件就可以实现每个的</t>
         </r>
@@ -1156,7 +1224,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1166,7 +1235,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>功能了。</t>
         </r>
@@ -1176,7 +1246,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1187,7 +1258,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>添加</t>
         </r>
@@ -1197,7 +1269,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SceneType</t>
         </r>
@@ -1207,7 +1280,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>需要在</t>
         </r>
@@ -1217,7 +1291,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SceneTypeConfig</t>
         </r>
@@ -1227,7 +1302,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>工作簿里增加，当前表格下面的</t>
         </r>
@@ -1272,7 +1348,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用于表示当前</t>
         </r>
@@ -1282,7 +1359,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1292,7 +1370,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>对客户端的网络协议。</t>
         </r>
@@ -1302,7 +1381,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1313,7 +1393,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Fantasy</t>
         </r>
@@ -1323,7 +1404,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>是以</t>
         </r>
@@ -1333,7 +1415,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1343,7 +1426,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>为单位的，所以网络协议是在</t>
         </r>
@@ -1353,7 +1437,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1363,7 +1448,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>里设置。</t>
         </r>
@@ -1373,7 +1459,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1384,7 +1471,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>比如做一个注册的</t>
         </r>
@@ -1394,7 +1482,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1404,7 +1493,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>，这里设置了协议类型和外网端口号、客户端就可以通过这个端口号来进行通讯。</t>
         </r>
@@ -1414,7 +1504,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1425,7 +1516,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>外网通讯的地址是在</t>
         </r>
@@ -1435,7 +1527,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>MachineConfig</t>
         </r>
@@ -1445,7 +1538,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>里设置的、因为这个</t>
         </r>
@@ -1455,7 +1549,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Scene</t>
         </r>
@@ -1465,7 +1560,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>是关联到</t>
         </r>
@@ -1475,7 +1571,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>ServerConfig</t>
         </r>
@@ -1485,7 +1582,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>下的，框架会自动根据</t>
         </r>
@@ -1543,7 +1641,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用来表示监听的外网连接的端口号，这里不填写或填</t>
         </r>
@@ -1553,7 +1652,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>0.</t>
         </r>
@@ -1563,7 +1663,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>表示不会建立监听，也就是不会接收到外网发送的消息</t>
         </r>
@@ -1577,7 +1678,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>用来表示监听的内部网络连接的端口号，这里不填写或填</t>
         </r>
@@ -1587,7 +1689,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>0.</t>
         </r>
@@ -1597,7 +1700,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>表示不会建立监听，也就是不会接受内部网络发送的消息</t>
         </r>
@@ -1611,7 +1715,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>根据</t>
         </r>
@@ -1621,7 +1726,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SceneTypeString</t>
         </r>
@@ -1631,7 +1737,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>列的值使用公式自动生成的，不需要手动修改。如果要修改在</t>
         </r>
@@ -1641,7 +1748,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SceneTypeString</t>
         </r>
@@ -1651,7 +1759,8 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>列选择就可以了</t>
         </r>
@@ -1701,9 +1810,6 @@
   </si>
   <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>NetworkProtocol</t>
   </si>
   <si>
     <t>OuterPort</t>
@@ -1833,9 +1939,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>KCP</t>
-  </si>
-  <si>
     <t>Addressable</t>
   </si>
   <si>
@@ -1862,6 +1965,14 @@
   </si>
   <si>
     <t>Chat服务器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NetworkProtocol</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCP</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1923,14 +2034,16 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1967,7 +2080,8 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2524,21 +2638,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="1" max="1" width="21.19921875" customWidth="1"/>
     <col min="3" max="3" width="51.5" customWidth="1"/>
     <col min="4" max="4" width="26.5" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" customWidth="1"/>
+    <col min="5" max="5" width="46.69921875" customWidth="1"/>
     <col min="6" max="6" width="162.5" customWidth="1"/>
-    <col min="7" max="7" width="84.33203125" customWidth="1"/>
+    <col min="7" max="7" width="84.296875" customWidth="1"/>
     <col min="8" max="8" width="120" customWidth="1"/>
     <col min="9" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
-    <col min="12" max="12" width="21.1640625" customWidth="1"/>
+    <col min="11" max="11" width="21.69921875" customWidth="1"/>
+    <col min="12" max="12" width="21.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="80" customHeight="1">
+    <row r="1" spans="1:12" ht="79.95" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2546,19 +2660,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>3</v>
@@ -2570,7 +2684,7 @@
         <v>2</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="2">
         <v>0</v>
@@ -2591,7 +2705,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="18">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="17.399999999999999">
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2626,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="18">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="17.399999999999999">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2634,16 +2748,16 @@
         <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>8</v>
@@ -2652,16 +2766,16 @@
         <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="16">
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
@@ -2669,36 +2783,36 @@
         <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="100.05" customHeight="1">
+      <c r="B6" s="5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="100" customHeight="1">
-      <c r="B6" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
@@ -2711,7 +2825,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="16">
+    <row r="7" spans="1:12" s="1" customFormat="1">
       <c r="B7" s="6">
         <v>1</v>
       </c>
@@ -2725,10 +2839,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -2740,10 +2854,10 @@
         <v>2</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="16">
+    <row r="8" spans="1:12" s="1" customFormat="1">
       <c r="B8" s="6">
         <f>B7+1</f>
         <v>2</v>
@@ -2758,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I8" s="7">
         <v>20000</v>
@@ -2777,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="16">
+    <row r="9" spans="1:12" s="1" customFormat="1">
       <c r="B9" s="6">
         <f>B8+1</f>
         <v>3</v>
@@ -2795,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -2810,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="16">
+    <row r="10" spans="1:12" s="1" customFormat="1">
       <c r="B10" s="6">
         <f>B9+1</f>
         <v>4</v>
@@ -2828,10 +2942,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -2843,7 +2957,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2879,128 +2993,128 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4E656C-FB27-224C-BBD7-96AC8FAF4A12}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="21.1640625" customWidth="1"/>
+    <col min="3" max="3" width="21.19921875" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="2" spans="1:3" s="1" customFormat="1">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="3" spans="1:3" s="1" customFormat="1">
       <c r="A3" s="7">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="4" spans="1:3" s="1" customFormat="1">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="5" spans="1:3" s="1" customFormat="1">
       <c r="A5" s="7">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="6" spans="1:3" s="1" customFormat="1">
       <c r="A6" s="7">
         <f t="shared" ref="A6:A10" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="7" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="7" spans="1:3" s="1" customFormat="1">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="8" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="8" spans="1:3" s="1" customFormat="1">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="9" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="9" spans="1:3" s="1" customFormat="1">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="1" customFormat="1" ht="16">
+    <row r="10" spans="1:3" s="1" customFormat="1">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
